--- a/output/pdf_financials_xlsx/GLOW.xlsx
+++ b/output/pdf_financials_xlsx/GLOW.xlsx
@@ -2183,16 +2183,16 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>3.077081</v>
+        <v>3.325236</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0.587383</v>
+        <v>3.325236</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>2.120237</v>
+        <v>5.799591</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>2.381829</v>
+        <v>5.663916</v>
       </c>
     </row>
     <row r="93">
@@ -4028,7 +4028,11 @@
           <t>Share-based payment reserve (note 16b)</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr"/>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E29" t="inlineStr">
         <is>
           <t>-</t>
@@ -4062,7 +4066,11 @@
           <t>Warrant reserve (note 16c)</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr"/>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E30" t="inlineStr">
         <is>
           <t>-</t>
@@ -4556,7 +4564,11 @@
           <t>Share-based payment reserve (note 15b)</t>
         </is>
       </c>
-      <c r="D44" t="inlineStr"/>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E44" t="inlineStr">
         <is>
           <t>-</t>
@@ -4590,7 +4602,11 @@
           <t>Warrant reserve (note 15c)</t>
         </is>
       </c>
-      <c r="D45" t="inlineStr"/>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E45" t="inlineStr">
         <is>
           <t>-</t>
@@ -4980,7 +4996,11 @@
           <t>Warrant reserve (note 14c)</t>
         </is>
       </c>
-      <c r="D56" t="inlineStr"/>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E56" s="5" t="n">
         <v>0.248155</v>
       </c>

--- a/output/pdf_financials_xlsx/GLOW.xlsx
+++ b/output/pdf_financials_xlsx/GLOW.xlsx
@@ -605,16 +605,16 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>0.748546</v>
+        <v>1.896289</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>0.508402</v>
+        <v>1.611972</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>0.5657799999999999</v>
+        <v>2.123826</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>0.601043</v>
+        <v>2.089998</v>
       </c>
     </row>
     <row r="11">
@@ -7350,7 +7350,11 @@
           <t>General and adminstrative expenses</t>
         </is>
       </c>
-      <c r="D123" t="inlineStr"/>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>GeneralAndAdministrativeExpense</t>
+        </is>
+      </c>
       <c r="E123" t="inlineStr">
         <is>
           <t>-</t>
@@ -7520,7 +7524,7 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
@@ -8692,7 +8696,7 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E161" s="5" t="n">

--- a/output/pdf_financials_xlsx/GLOW.xlsx
+++ b/output/pdf_financials_xlsx/GLOW.xlsx
@@ -586,10 +586,10 @@
         </is>
       </c>
       <c r="B9" s="3" t="n">
-        <v>0.039505</v>
+        <v>0.091475</v>
       </c>
       <c r="C9" s="3" t="n">
-        <v>0</v>
+        <v>0.037655</v>
       </c>
       <c r="D9" s="3" t="n">
         <v>0</v>
@@ -8444,7 +8444,11 @@
           <t>Occupancy costs</t>
         </is>
       </c>
-      <c r="D154" t="inlineStr"/>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>OtherOperatingExpenses</t>
+        </is>
+      </c>
       <c r="E154" s="5" t="n">
         <v>0.05197</v>
       </c>

--- a/output/pdf_financials_xlsx/GLOW.xlsx
+++ b/output/pdf_financials_xlsx/GLOW.xlsx
@@ -6606,7 +6606,11 @@
           <t>Proceeds on sale of investments</t>
         </is>
       </c>
-      <c r="D102" t="inlineStr"/>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E102" t="inlineStr">
         <is>
           <t>-</t>
